--- a/engine/phdc_study/PHDC_Valuation_Model_17092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_17092026.xlsx
@@ -5296,7 +5296,7 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Net debt per share, 31 March 2026 (EGP)</t>
+          <t>Net debt per share, 30 June 2026 (EGP)</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
@@ -5923,7 +5923,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Present value of the explicit five years</t>
+          <t>Present value of the explicit 15 years</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
@@ -5954,7 +5954,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>less net debt, 31 March 2026</t>
+          <t>less net debt, 30 June 2026</t>
         </is>
       </c>
       <c r="B7" s="10">
@@ -6152,11 +6152,11 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.3832237248431056</v>
+        <v>0.3546692094355787</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>average of FY2025 and 1Q2026 as reported</t>
+          <t>anchored on the latest reviewed period, 1H2026, six months ended 30 June 2026 — the rate the model runs</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>gross borrowings less cash, 31 March 2026 reviewed balance sheet</t>
+          <t>gross borrowings less cash, 30 June 2026 reviewed balance sheet</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31 March 2026 reviewed balance sheet</t>
+          <t>30 June 2026 reviewed balance sheet</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31 March 2026 reviewed balance sheet</t>
+          <t>30 June 2026 reviewed balance sheet</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>as at 31 March 2026</t>
+          <t>as at 30 June 2026</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>h1 2026 results</t>
+          <t>h1 2026 release operating drivers</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>As at this build date (30-Aug-2026) no 2Q/H1-2026 statements or release are posted to the result centre; the newest disclosure of any kind is 1Q2026 (posted 25-Jun-2026). The study</t>
+          <t xml:space="preserve">The reviewed consolidated statements for the six months ended 30 June 2026 ARE held and are what the bridge, the gross-margin anchor and the cash-conversion rate stand on. What is </t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Investments in associates, 31 March 2026</t>
+          <t>Investments in associates, 30 June 2026</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
@@ -6519,7 +6519,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Investment property, 31 March 2026</t>
+          <t>Investment property, 30 June 2026</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
@@ -6529,7 +6529,7 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Cash, 31 March 2026</t>
+          <t>Cash, 30 June 2026</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
@@ -6539,7 +6539,7 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Gross borrowings, 31 March 2026</t>
+          <t>Gross borrowings, 30 June 2026</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
@@ -8252,7 +8252,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gross margin is an OUTPUT of price per unit against cost per unit.</t>
+          <t>Gross margin is ANCHORED on the latest reviewed period and cost per unit is solved from it; the company discloses no unit count after FY2024, so there is no independent cost per unit to build. See the study, section 1.1.</t>
         </is>
       </c>
     </row>

--- a/engine/phdc_study/PHDC_Valuation_Model_17092026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_17092026.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,13 +130,12 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -574,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -633,7 +632,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>65900.2</v>
+        <v>65900.163</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>54166.4</v>
@@ -646,7 +645,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>106229.6</v>
+        <v>106229.649</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>69270.89999999999</v>
@@ -659,7 +658,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>172129.8</v>
+        <v>172129.829</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>123437.3</v>
@@ -672,7 +671,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>105099</v>
+        <v>105098.969</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>74496.89999999999</v>
@@ -685,7 +684,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>48265.1</v>
+        <v>48265.091</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>34315.7</v>
@@ -698,7 +697,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>153364.1</v>
+        <v>153364.06</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>108812.6</v>
@@ -711,7 +710,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>18765.8</v>
+        <v>18765.751</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>14624.7</v>
@@ -1110,49 +1109,49 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="C22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="D22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="J22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="K22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="L22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="M22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="N22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="O22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="P22" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
     </row>
     <row r="23">
@@ -1161,50 +1160,70 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n">
-        <v>174203.5663</v>
-      </c>
-      <c r="C23" s="22" t="n">
-        <v>178589.6446</v>
-      </c>
-      <c r="D23" s="22" t="n">
-        <v>185428.1321</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>194876.5103</v>
-      </c>
-      <c r="F23" s="22" t="n">
-        <v>207133.7119</v>
-      </c>
-      <c r="G23" s="22" t="n">
-        <v>222419.6183</v>
-      </c>
-      <c r="H23" s="22" t="n">
-        <v>240896.9851</v>
-      </c>
-      <c r="I23" s="22" t="n">
-        <v>262653.1883</v>
-      </c>
-      <c r="J23" s="22" t="n">
-        <v>287683.4814</v>
-      </c>
-      <c r="K23" s="22" t="n">
-        <v>315877.3825</v>
-      </c>
-      <c r="L23" s="22" t="n">
-        <v>347009.8047</v>
-      </c>
-      <c r="M23" s="22" t="n">
-        <v>380738.3531</v>
-      </c>
-      <c r="N23" s="22" t="n">
-        <v>417244.7565</v>
-      </c>
-      <c r="O23" s="22" t="n">
-        <v>456723.4648</v>
-      </c>
-      <c r="P23" s="22" t="n">
-        <v>499382.5393</v>
+      <c r="B23" s="22">
+        <f>B16+B17+B18+B19+B20+B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="22">
+        <f>C16+C17+C18+C19+C20+C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="22">
+        <f>D16+D17+D18+D19+D20+D21+D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="22">
+        <f>E16+E17+E18+E19+E20+E21+E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="22">
+        <f>F16+F17+F18+F19+F20+F21+F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="22">
+        <f>G16+G17+G18+G19+G20+G21+G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="22">
+        <f>H16+H17+H18+H19+H20+H21+H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="22">
+        <f>I16+I17+I18+I19+I20+I21+I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="22">
+        <f>J16+J17+J18+J19+J20+J21+J22</f>
+        <v/>
+      </c>
+      <c r="K23" s="22">
+        <f>K16+K17+K18+K19+K20+K21+K22</f>
+        <v/>
+      </c>
+      <c r="L23" s="22">
+        <f>L16+L17+L18+L19+L20+L21+L22</f>
+        <v/>
+      </c>
+      <c r="M23" s="22">
+        <f>M16+M17+M18+M19+M20+M21+M22</f>
+        <v/>
+      </c>
+      <c r="N23" s="22">
+        <f>N16+N17+N18+N19+N20+N21+N22</f>
+        <v/>
+      </c>
+      <c r="O23" s="22">
+        <f>O16+O17+O18+O19+O20+O21+O22</f>
+        <v/>
+      </c>
+      <c r="P23" s="22">
+        <f>P16+P17+P18+P19+P20+P21+P22</f>
+        <v/>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>the seven asset rows above, summed in the cell</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1474,49 +1493,49 @@
         </is>
       </c>
       <c r="B29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="C29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="D29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="J29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="K29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="L29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="M29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="N29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="O29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="P29" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
     </row>
     <row r="30">
@@ -1525,50 +1544,70 @@
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n">
-        <v>152775.8773</v>
-      </c>
-      <c r="C30" s="22" t="n">
-        <v>152986.2806</v>
-      </c>
-      <c r="D30" s="22" t="n">
-        <v>154043.5905</v>
-      </c>
-      <c r="E30" s="22" t="n">
-        <v>156002.1912</v>
-      </c>
-      <c r="F30" s="22" t="n">
-        <v>158930.7814</v>
-      </c>
-      <c r="G30" s="22" t="n">
-        <v>162905.2943</v>
-      </c>
-      <c r="H30" s="22" t="n">
-        <v>167981.9352</v>
-      </c>
-      <c r="I30" s="22" t="n">
-        <v>174190.8783</v>
-      </c>
-      <c r="J30" s="22" t="n">
-        <v>181530.4844</v>
-      </c>
-      <c r="K30" s="22" t="n">
-        <v>189962.6002</v>
-      </c>
-      <c r="L30" s="22" t="n">
-        <v>199409.4949</v>
-      </c>
-      <c r="M30" s="22" t="n">
-        <v>209752.9269</v>
-      </c>
-      <c r="N30" s="22" t="n">
-        <v>221055.654</v>
-      </c>
-      <c r="O30" s="22" t="n">
-        <v>233384.8267</v>
-      </c>
-      <c r="P30" s="22" t="n">
-        <v>246812.2963</v>
+      <c r="B30" s="22">
+        <f>B24+B25+B26+B27+B28+B29</f>
+        <v/>
+      </c>
+      <c r="C30" s="22">
+        <f>C24+C25+C26+C27+C28+C29</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>D24+D25+D26+D27+D28+D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="22">
+        <f>E24+E25+E26+E27+E28+E29</f>
+        <v/>
+      </c>
+      <c r="F30" s="22">
+        <f>F24+F25+F26+F27+F28+F29</f>
+        <v/>
+      </c>
+      <c r="G30" s="22">
+        <f>G24+G25+G26+G27+G28+G29</f>
+        <v/>
+      </c>
+      <c r="H30" s="22">
+        <f>H24+H25+H26+H27+H28+H29</f>
+        <v/>
+      </c>
+      <c r="I30" s="22">
+        <f>I24+I25+I26+I27+I28+I29</f>
+        <v/>
+      </c>
+      <c r="J30" s="22">
+        <f>J24+J25+J26+J27+J28+J29</f>
+        <v/>
+      </c>
+      <c r="K30" s="22">
+        <f>K24+K25+K26+K27+K28+K29</f>
+        <v/>
+      </c>
+      <c r="L30" s="22">
+        <f>L24+L25+L26+L27+L28+L29</f>
+        <v/>
+      </c>
+      <c r="M30" s="22">
+        <f>M24+M25+M26+M27+M28+M29</f>
+        <v/>
+      </c>
+      <c r="N30" s="22">
+        <f>N24+N25+N26+N27+N28+N29</f>
+        <v/>
+      </c>
+      <c r="O30" s="22">
+        <f>O24+O25+O26+O27+O28+O29</f>
+        <v/>
+      </c>
+      <c r="P30" s="22">
+        <f>P24+P25+P26+P27+P28+P29</f>
+        <v/>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>the six liability rows above, summed in the cell</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1578,49 +1617,49 @@
         </is>
       </c>
       <c r="B31" s="21" t="n">
-        <v>21427.689</v>
+        <v>21427.64</v>
       </c>
       <c r="C31" s="21" t="n">
-        <v>25603.364</v>
+        <v>25603.315</v>
       </c>
       <c r="D31" s="21" t="n">
-        <v>31384.5416</v>
+        <v>31384.4926</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>38874.3191</v>
+        <v>38874.2701</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>48202.9305</v>
+        <v>48202.8815</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>59514.324</v>
+        <v>59514.275</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>72915.05</v>
+        <v>72915.001</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>88462.3101</v>
+        <v>88462.2611</v>
       </c>
       <c r="J31" s="21" t="n">
-        <v>106152.9969</v>
+        <v>106152.9479</v>
       </c>
       <c r="K31" s="21" t="n">
-        <v>125914.7823</v>
+        <v>125914.7333</v>
       </c>
       <c r="L31" s="21" t="n">
-        <v>147600.3098</v>
+        <v>147600.2608</v>
       </c>
       <c r="M31" s="21" t="n">
-        <v>170985.4262</v>
+        <v>170985.3772</v>
       </c>
       <c r="N31" s="21" t="n">
-        <v>196189.1025</v>
+        <v>196189.0535</v>
       </c>
       <c r="O31" s="21" t="n">
-        <v>223338.6381</v>
+        <v>223338.5891</v>
       </c>
       <c r="P31" s="21" t="n">
-        <v>252570.2431</v>
+        <v>252570.1941</v>
       </c>
     </row>
     <row r="32">
@@ -1629,50 +1668,65 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B32" s="22" t="n">
-        <v>174203.5663</v>
-      </c>
-      <c r="C32" s="22" t="n">
-        <v>178589.6446</v>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>185428.1321</v>
-      </c>
-      <c r="E32" s="22" t="n">
-        <v>194876.5103</v>
-      </c>
-      <c r="F32" s="22" t="n">
-        <v>207133.7119</v>
-      </c>
-      <c r="G32" s="22" t="n">
-        <v>222419.6183</v>
-      </c>
-      <c r="H32" s="22" t="n">
-        <v>240896.9851</v>
-      </c>
-      <c r="I32" s="22" t="n">
-        <v>262653.1883</v>
-      </c>
-      <c r="J32" s="22" t="n">
-        <v>287683.4814</v>
-      </c>
-      <c r="K32" s="22" t="n">
-        <v>315877.3825</v>
-      </c>
-      <c r="L32" s="22" t="n">
-        <v>347009.8047</v>
-      </c>
-      <c r="M32" s="22" t="n">
-        <v>380738.3531</v>
-      </c>
-      <c r="N32" s="22" t="n">
-        <v>417244.7565</v>
-      </c>
-      <c r="O32" s="22" t="n">
-        <v>456723.4648</v>
-      </c>
-      <c r="P32" s="22" t="n">
-        <v>499382.5393</v>
+      <c r="B32" s="22">
+        <f>B30+B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="22">
+        <f>C30+C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="22">
+        <f>D30+D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="22">
+        <f>E30+E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="22">
+        <f>F30+F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="22">
+        <f>G30+G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="22">
+        <f>H30+H31</f>
+        <v/>
+      </c>
+      <c r="I32" s="22">
+        <f>I30+I31</f>
+        <v/>
+      </c>
+      <c r="J32" s="22">
+        <f>J30+J31</f>
+        <v/>
+      </c>
+      <c r="K32" s="22">
+        <f>K30+K31</f>
+        <v/>
+      </c>
+      <c r="L32" s="22">
+        <f>L30+L31</f>
+        <v/>
+      </c>
+      <c r="M32" s="22">
+        <f>M30+M31</f>
+        <v/>
+      </c>
+      <c r="N32" s="22">
+        <f>N30+N31</f>
+        <v/>
+      </c>
+      <c r="O32" s="22">
+        <f>O30+O31</f>
+        <v/>
+      </c>
+      <c r="P32" s="22">
+        <f>P30+P31</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1681,50 +1735,70 @@
           <t>Check: assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="E33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="G33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O33" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="27" t="n">
-        <v>0</v>
+      <c r="B33" s="25">
+        <f>B23-B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="25">
+        <f>C23-C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="25">
+        <f>D23-D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="25">
+        <f>E23-E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="25">
+        <f>F23-F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="25">
+        <f>G23-G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="25">
+        <f>H23-H32</f>
+        <v/>
+      </c>
+      <c r="I33" s="25">
+        <f>I23-I32</f>
+        <v/>
+      </c>
+      <c r="J33" s="25">
+        <f>J23-J32</f>
+        <v/>
+      </c>
+      <c r="K33" s="25">
+        <f>K23-K32</f>
+        <v/>
+      </c>
+      <c r="L33" s="25">
+        <f>L23-L32</f>
+        <v/>
+      </c>
+      <c r="M33" s="25">
+        <f>M23-M32</f>
+        <v/>
+      </c>
+      <c r="N33" s="25">
+        <f>N23-N32</f>
+        <v/>
+      </c>
+      <c r="O33" s="25">
+        <f>O23-O32</f>
+        <v/>
+      </c>
+      <c r="P33" s="25">
+        <f>P23-P32</f>
+        <v/>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>A LIVE CHECK: two sums subtracted. It used to be the model's own computed difference, which is a check that cannot fail</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2417,49 +2491,49 @@
         </is>
       </c>
       <c r="B49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="C49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="D49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="F49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="G49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="H49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="I49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="J49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="K49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="L49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="M49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="N49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="O49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
       <c r="P49" s="21" t="n">
-        <v>15128.3</v>
+        <v>15128.329</v>
       </c>
     </row>
     <row r="50">
@@ -2468,50 +2542,70 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="B50" s="22" t="n">
-        <v>183965.1445</v>
-      </c>
-      <c r="C50" s="22" t="n">
-        <v>227222.9855</v>
-      </c>
-      <c r="D50" s="22" t="n">
-        <v>275899.7431</v>
-      </c>
-      <c r="E50" s="22" t="n">
-        <v>327704.264</v>
-      </c>
-      <c r="F50" s="22" t="n">
-        <v>383459.2698</v>
-      </c>
-      <c r="G50" s="22" t="n">
-        <v>443580.6913</v>
-      </c>
-      <c r="H50" s="22" t="n">
-        <v>506935.1708</v>
-      </c>
-      <c r="I50" s="22" t="n">
-        <v>572027.0651</v>
-      </c>
-      <c r="J50" s="22" t="n">
-        <v>637028.4056000001</v>
-      </c>
-      <c r="K50" s="22" t="n">
-        <v>699840.9901000001</v>
-      </c>
-      <c r="L50" s="22" t="n">
-        <v>758190.4845</v>
-      </c>
-      <c r="M50" s="22" t="n">
-        <v>810647.9174</v>
-      </c>
-      <c r="N50" s="22" t="n">
-        <v>866958.9725</v>
-      </c>
-      <c r="O50" s="22" t="n">
-        <v>927393.4033</v>
-      </c>
-      <c r="P50" s="22" t="n">
-        <v>992239.8462</v>
+      <c r="B50" s="22">
+        <f>B43+B44+B45+B46+B47+B48+B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="22">
+        <f>C43+C44+C45+C46+C47+C48+C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="22">
+        <f>D43+D44+D45+D46+D47+D48+D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="22">
+        <f>E43+E44+E45+E46+E47+E48+E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="22">
+        <f>F43+F44+F45+F46+F47+F48+F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="22">
+        <f>G43+G44+G45+G46+G47+G48+G49</f>
+        <v/>
+      </c>
+      <c r="H50" s="22">
+        <f>H43+H44+H45+H46+H47+H48+H49</f>
+        <v/>
+      </c>
+      <c r="I50" s="22">
+        <f>I43+I44+I45+I46+I47+I48+I49</f>
+        <v/>
+      </c>
+      <c r="J50" s="22">
+        <f>J43+J44+J45+J46+J47+J48+J49</f>
+        <v/>
+      </c>
+      <c r="K50" s="22">
+        <f>K43+K44+K45+K46+K47+K48+K49</f>
+        <v/>
+      </c>
+      <c r="L50" s="22">
+        <f>L43+L44+L45+L46+L47+L48+L49</f>
+        <v/>
+      </c>
+      <c r="M50" s="22">
+        <f>M43+M44+M45+M46+M47+M48+M49</f>
+        <v/>
+      </c>
+      <c r="N50" s="22">
+        <f>N43+N44+N45+N46+N47+N48+N49</f>
+        <v/>
+      </c>
+      <c r="O50" s="22">
+        <f>O43+O44+O45+O46+O47+O48+O49</f>
+        <v/>
+      </c>
+      <c r="P50" s="22">
+        <f>P43+P44+P45+P46+P47+P48+P49</f>
+        <v/>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>the seven asset rows above, summed in the cell</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2781,49 +2875,49 @@
         </is>
       </c>
       <c r="B56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="C56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="D56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="F56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="H56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="I56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="J56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="K56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="L56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="M56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="N56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="O56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
       <c r="P56" s="21" t="n">
-        <v>39074.8</v>
+        <v>39074.878</v>
       </c>
     </row>
     <row r="57">
@@ -2832,50 +2926,70 @@
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="B57" s="22" t="n">
-        <v>162537.4555</v>
-      </c>
-      <c r="C57" s="22" t="n">
-        <v>201619.6215</v>
-      </c>
-      <c r="D57" s="22" t="n">
-        <v>244515.2016</v>
-      </c>
-      <c r="E57" s="22" t="n">
-        <v>288829.9449</v>
-      </c>
-      <c r="F57" s="22" t="n">
-        <v>335256.3393</v>
-      </c>
-      <c r="G57" s="22" t="n">
-        <v>384066.3672</v>
-      </c>
-      <c r="H57" s="22" t="n">
-        <v>434020.1208</v>
-      </c>
-      <c r="I57" s="22" t="n">
-        <v>483564.755</v>
-      </c>
-      <c r="J57" s="22" t="n">
-        <v>530875.4086</v>
-      </c>
-      <c r="K57" s="22" t="n">
-        <v>573926.2078</v>
-      </c>
-      <c r="L57" s="22" t="n">
-        <v>610590.1747</v>
-      </c>
-      <c r="M57" s="22" t="n">
-        <v>639662.4913</v>
-      </c>
-      <c r="N57" s="22" t="n">
-        <v>670769.87</v>
-      </c>
-      <c r="O57" s="22" t="n">
-        <v>704054.7652</v>
-      </c>
-      <c r="P57" s="22" t="n">
-        <v>739669.6030999999</v>
+      <c r="B57" s="22">
+        <f>B51+B52+B53+B54+B55+B56</f>
+        <v/>
+      </c>
+      <c r="C57" s="22">
+        <f>C51+C52+C53+C54+C55+C56</f>
+        <v/>
+      </c>
+      <c r="D57" s="22">
+        <f>D51+D52+D53+D54+D55+D56</f>
+        <v/>
+      </c>
+      <c r="E57" s="22">
+        <f>E51+E52+E53+E54+E55+E56</f>
+        <v/>
+      </c>
+      <c r="F57" s="22">
+        <f>F51+F52+F53+F54+F55+F56</f>
+        <v/>
+      </c>
+      <c r="G57" s="22">
+        <f>G51+G52+G53+G54+G55+G56</f>
+        <v/>
+      </c>
+      <c r="H57" s="22">
+        <f>H51+H52+H53+H54+H55+H56</f>
+        <v/>
+      </c>
+      <c r="I57" s="22">
+        <f>I51+I52+I53+I54+I55+I56</f>
+        <v/>
+      </c>
+      <c r="J57" s="22">
+        <f>J51+J52+J53+J54+J55+J56</f>
+        <v/>
+      </c>
+      <c r="K57" s="22">
+        <f>K51+K52+K53+K54+K55+K56</f>
+        <v/>
+      </c>
+      <c r="L57" s="22">
+        <f>L51+L52+L53+L54+L55+L56</f>
+        <v/>
+      </c>
+      <c r="M57" s="22">
+        <f>M51+M52+M53+M54+M55+M56</f>
+        <v/>
+      </c>
+      <c r="N57" s="22">
+        <f>N51+N52+N53+N54+N55+N56</f>
+        <v/>
+      </c>
+      <c r="O57" s="22">
+        <f>O51+O52+O53+O54+O55+O56</f>
+        <v/>
+      </c>
+      <c r="P57" s="22">
+        <f>P51+P52+P53+P54+P55+P56</f>
+        <v/>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>the six liability rows above, summed in the cell</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -2885,49 +2999,49 @@
         </is>
       </c>
       <c r="B58" s="21" t="n">
-        <v>21427.689</v>
+        <v>21427.64</v>
       </c>
       <c r="C58" s="21" t="n">
-        <v>25603.364</v>
+        <v>25603.315</v>
       </c>
       <c r="D58" s="21" t="n">
-        <v>31384.5416</v>
+        <v>31384.4926</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>38874.3191</v>
+        <v>38874.2701</v>
       </c>
       <c r="F58" s="21" t="n">
-        <v>48202.9305</v>
+        <v>48202.8815</v>
       </c>
       <c r="G58" s="21" t="n">
-        <v>59514.324</v>
+        <v>59514.275</v>
       </c>
       <c r="H58" s="21" t="n">
-        <v>72915.05</v>
+        <v>72915.001</v>
       </c>
       <c r="I58" s="21" t="n">
-        <v>88462.3101</v>
+        <v>88462.2611</v>
       </c>
       <c r="J58" s="21" t="n">
-        <v>106152.9969</v>
+        <v>106152.9479</v>
       </c>
       <c r="K58" s="21" t="n">
-        <v>125914.7823</v>
+        <v>125914.7333</v>
       </c>
       <c r="L58" s="21" t="n">
-        <v>147600.3098</v>
+        <v>147600.2608</v>
       </c>
       <c r="M58" s="21" t="n">
-        <v>170985.4262</v>
+        <v>170985.3772</v>
       </c>
       <c r="N58" s="21" t="n">
-        <v>196189.1025</v>
+        <v>196189.0535</v>
       </c>
       <c r="O58" s="21" t="n">
-        <v>223338.6381</v>
+        <v>223338.5891</v>
       </c>
       <c r="P58" s="21" t="n">
-        <v>252570.2431</v>
+        <v>252570.1941</v>
       </c>
     </row>
     <row r="59">
@@ -2936,50 +3050,65 @@
           <t>TOTAL LIABILITIES AND EQUITY</t>
         </is>
       </c>
-      <c r="B59" s="22" t="n">
-        <v>183965.1445</v>
-      </c>
-      <c r="C59" s="22" t="n">
-        <v>227222.9855</v>
-      </c>
-      <c r="D59" s="22" t="n">
-        <v>275899.7431</v>
-      </c>
-      <c r="E59" s="22" t="n">
-        <v>327704.264</v>
-      </c>
-      <c r="F59" s="22" t="n">
-        <v>383459.2698</v>
-      </c>
-      <c r="G59" s="22" t="n">
-        <v>443580.6913</v>
-      </c>
-      <c r="H59" s="22" t="n">
-        <v>506935.1708</v>
-      </c>
-      <c r="I59" s="22" t="n">
-        <v>572027.0651</v>
-      </c>
-      <c r="J59" s="22" t="n">
-        <v>637028.4056000001</v>
-      </c>
-      <c r="K59" s="22" t="n">
-        <v>699840.9901000001</v>
-      </c>
-      <c r="L59" s="22" t="n">
-        <v>758190.4845</v>
-      </c>
-      <c r="M59" s="22" t="n">
-        <v>810647.9174</v>
-      </c>
-      <c r="N59" s="22" t="n">
-        <v>866958.9725</v>
-      </c>
-      <c r="O59" s="22" t="n">
-        <v>927393.4033</v>
-      </c>
-      <c r="P59" s="22" t="n">
-        <v>992239.8462</v>
+      <c r="B59" s="22">
+        <f>B57+B58</f>
+        <v/>
+      </c>
+      <c r="C59" s="22">
+        <f>C57+C58</f>
+        <v/>
+      </c>
+      <c r="D59" s="22">
+        <f>D57+D58</f>
+        <v/>
+      </c>
+      <c r="E59" s="22">
+        <f>E57+E58</f>
+        <v/>
+      </c>
+      <c r="F59" s="22">
+        <f>F57+F58</f>
+        <v/>
+      </c>
+      <c r="G59" s="22">
+        <f>G57+G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="22">
+        <f>H57+H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="22">
+        <f>I57+I58</f>
+        <v/>
+      </c>
+      <c r="J59" s="22">
+        <f>J57+J58</f>
+        <v/>
+      </c>
+      <c r="K59" s="22">
+        <f>K57+K58</f>
+        <v/>
+      </c>
+      <c r="L59" s="22">
+        <f>L57+L58</f>
+        <v/>
+      </c>
+      <c r="M59" s="22">
+        <f>M57+M58</f>
+        <v/>
+      </c>
+      <c r="N59" s="22">
+        <f>N57+N58</f>
+        <v/>
+      </c>
+      <c r="O59" s="22">
+        <f>O57+O58</f>
+        <v/>
+      </c>
+      <c r="P59" s="22">
+        <f>P57+P58</f>
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -2988,50 +3117,70 @@
           <t>Check: assets less liabilities and equity</t>
         </is>
       </c>
-      <c r="B60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="C60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K60" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="N60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="O60" s="27" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P60" s="27" t="n">
-        <v>0</v>
+      <c r="B60" s="25">
+        <f>B50-B59</f>
+        <v/>
+      </c>
+      <c r="C60" s="25">
+        <f>C50-C59</f>
+        <v/>
+      </c>
+      <c r="D60" s="25">
+        <f>D50-D59</f>
+        <v/>
+      </c>
+      <c r="E60" s="25">
+        <f>E50-E59</f>
+        <v/>
+      </c>
+      <c r="F60" s="25">
+        <f>F50-F59</f>
+        <v/>
+      </c>
+      <c r="G60" s="25">
+        <f>G50-G59</f>
+        <v/>
+      </c>
+      <c r="H60" s="25">
+        <f>H50-H59</f>
+        <v/>
+      </c>
+      <c r="I60" s="25">
+        <f>I50-I59</f>
+        <v/>
+      </c>
+      <c r="J60" s="25">
+        <f>J50-J59</f>
+        <v/>
+      </c>
+      <c r="K60" s="25">
+        <f>K50-K59</f>
+        <v/>
+      </c>
+      <c r="L60" s="25">
+        <f>L50-L59</f>
+        <v/>
+      </c>
+      <c r="M60" s="25">
+        <f>M50-M59</f>
+        <v/>
+      </c>
+      <c r="N60" s="25">
+        <f>N50-N59</f>
+        <v/>
+      </c>
+      <c r="O60" s="25">
+        <f>O50-O59</f>
+        <v/>
+      </c>
+      <c r="P60" s="25">
+        <f>P50-P59</f>
+        <v/>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>A LIVE CHECK: two sums subtracted. It used to be the model's own computed difference, which is a check that cannot fail</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3455,7 +3604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3659,50 +3808,70 @@
           <t>Change in working capital, cash effect</t>
         </is>
       </c>
-      <c r="B8" s="21" t="n">
-        <v>453.9937</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <v>-162.4181</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>-816.1768</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-1511.9166</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-2260.6874</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-3068.0739</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-3918.8475</v>
-      </c>
-      <c r="I8" s="21" t="n">
-        <v>-4792.9136</v>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>-5665.7143</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-6509.063</v>
-      </c>
-      <c r="L8" s="21" t="n">
-        <v>-7292.4085</v>
-      </c>
-      <c r="M8" s="21" t="n">
-        <v>-7984.479</v>
-      </c>
-      <c r="N8" s="21" t="n">
-        <v>-8724.9944</v>
-      </c>
-      <c r="O8" s="21" t="n">
-        <v>-9517.3459</v>
-      </c>
-      <c r="P8" s="21" t="n">
-        <v>-10365.162</v>
+      <c r="B8" s="21">
+        <f>B9-'Income Statement'!B19-'Income Statement'!B15</f>
+        <v/>
+      </c>
+      <c r="C8" s="21">
+        <f>C9-'Income Statement'!C19-'Income Statement'!C15</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>D9-'Income Statement'!D19-'Income Statement'!D15</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>E9-'Income Statement'!E19-'Income Statement'!E15</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>F9-'Income Statement'!F19-'Income Statement'!F15</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>G9-'Income Statement'!G19-'Income Statement'!G15</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>H9-'Income Statement'!H19-'Income Statement'!H15</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>I9-'Income Statement'!I19-'Income Statement'!I15</f>
+        <v/>
+      </c>
+      <c r="J8" s="21">
+        <f>J9-'Income Statement'!J19-'Income Statement'!J15</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>K9-'Income Statement'!K19-'Income Statement'!K15</f>
+        <v/>
+      </c>
+      <c r="L8" s="21">
+        <f>L9-'Income Statement'!L19-'Income Statement'!L15</f>
+        <v/>
+      </c>
+      <c r="M8" s="21">
+        <f>M9-'Income Statement'!M19-'Income Statement'!M15</f>
+        <v/>
+      </c>
+      <c r="N8" s="21">
+        <f>N9-'Income Statement'!N19-'Income Statement'!N15</f>
+        <v/>
+      </c>
+      <c r="O8" s="21">
+        <f>O9-'Income Statement'!O19-'Income Statement'!O15</f>
+        <v/>
+      </c>
+      <c r="P8" s="21">
+        <f>P9-'Income Statement'!P19-'Income Statement'!P15</f>
+        <v/>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>THE PLUG. Operating cash is set and working capital is what is left, which is the whole difference between this framing and the one below</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -3711,50 +3880,70 @@
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n">
-        <v>3509.7709</v>
-      </c>
-      <c r="C9" s="22" t="n">
-        <v>4520.5849</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>5592.6416</v>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>6733.5405</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>7961.4016</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>9285.382600000001</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>10680.5114</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>12113.836</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>13545.0857</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>14928.039</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>16212.5967</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>17347.4785</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>18561.802</v>
-      </c>
-      <c r="O9" s="22" t="n">
-        <v>19861.1281</v>
-      </c>
-      <c r="P9" s="22" t="n">
-        <v>21251.4071</v>
+      <c r="B9" s="22">
+        <f>DCF!B9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="C9" s="22">
+        <f>DCF!C9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
+        <f>DCF!D9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E9" s="22">
+        <f>DCF!E9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="F9" s="22">
+        <f>DCF!F9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>DCF!G9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>DCF!H9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>DCF!I9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>DCF!J9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="K9" s="22">
+        <f>DCF!K9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>DCF!L9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="M9" s="22">
+        <f>DCF!M9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <f>DCF!N9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="O9" s="22">
+        <f>DCF!O9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="P9" s="22">
+        <f>DCF!P9*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>SET at the conversion rate times revenue — this is the crux input, and the row below proves the division</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -3763,50 +3952,70 @@
           <t xml:space="preserve">  as a share of revenue</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="F10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="G10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="L10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="N10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="O10" s="17" t="n">
-        <v>0.0871</v>
-      </c>
-      <c r="P10" s="17" t="n">
-        <v>0.0871</v>
+      <c r="B10" s="17">
+        <f>B9/DCF!B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>C9/DCF!C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>D9/DCF!D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>E9/DCF!E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>F9/DCF!F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>G9/DCF!G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>H9/DCF!H9</f>
+        <v/>
+      </c>
+      <c r="I10" s="17">
+        <f>I9/DCF!I9</f>
+        <v/>
+      </c>
+      <c r="J10" s="17">
+        <f>J9/DCF!J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>K9/DCF!K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="17">
+        <f>L9/DCF!L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="17">
+        <f>M9/DCF!M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="17">
+        <f>N9/DCF!N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="17">
+        <f>O9/DCF!O9</f>
+        <v/>
+      </c>
+      <c r="P10" s="17">
+        <f>P9/DCF!P9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>the conversion rate, recovered from the row above: flat by construction because operating cash is set as a share of revenue</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -3815,50 +4024,70 @@
           <t>Capital expenditure</t>
         </is>
       </c>
-      <c r="B11" s="21" t="n">
-        <v>-402.7893</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <v>-518.7927</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>-641.8244</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-772.7565</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-913.6686999999999</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-1065.6118</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>-1225.7199</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>-1390.2116</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>-1554.465</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>-1713.1759</v>
-      </c>
-      <c r="L11" s="21" t="n">
-        <v>-1860.5947</v>
-      </c>
-      <c r="M11" s="21" t="n">
-        <v>-1990.8364</v>
-      </c>
-      <c r="N11" s="21" t="n">
-        <v>-2130.1949</v>
-      </c>
-      <c r="O11" s="21" t="n">
-        <v>-2279.3085</v>
-      </c>
-      <c r="P11" s="21" t="n">
-        <v>-2438.8601</v>
+      <c r="B11" s="21">
+        <f>-DCF!B9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>-DCF!C9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>-DCF!D9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>-DCF!E9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>-DCF!F9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>-DCF!G9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>-DCF!H9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>-DCF!I9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>-DCF!J9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>-DCF!K9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
+        <f>-DCF!L9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
+        <f>-DCF!M9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>-DCF!N9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="O11" s="21">
+        <f>-DCF!O9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>-DCF!P9*Assumptions!$B$24</f>
+        <v/>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>maintenance only, at the share of revenue on the Assumptions sheet</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4661,7 +4890,7 @@
           <t>FY2023</t>
         </is>
       </c>
-      <c r="B31" s="28" t="n">
+      <c r="B31" s="26" t="n">
         <v>0.043334</v>
       </c>
     </row>
@@ -4671,7 +4900,7 @@
           <t>FY2024</t>
         </is>
       </c>
-      <c r="B32" s="28" t="n">
+      <c r="B32" s="26" t="n">
         <v>0.1787</v>
       </c>
     </row>
@@ -4681,7 +4910,7 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="B33" s="28" t="n">
+      <c r="B33" s="26" t="n">
         <v>0.039376</v>
       </c>
     </row>
@@ -4691,7 +4920,7 @@
           <t xml:space="preserve">  mean, carried above</t>
         </is>
       </c>
-      <c r="B34" s="28" t="n">
+      <c r="B34" s="26" t="n">
         <v>0.08713700000000001</v>
       </c>
     </row>
@@ -5102,19 +5331,19 @@
           <t>Cash conversion</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="27" t="n">
         <v>0.209647238833035</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="27" t="n">
         <v>0.229647238833035</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="27" t="n">
         <v>0.249647238833035</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="27" t="n">
         <v>0.269647238833035</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.2896472388330349</v>
       </c>
     </row>
@@ -5371,7 +5600,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -5418,19 +5647,19 @@
           <t>Talaat Moustafa Group Holding</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n">
+      <c r="C5" s="29" t="n">
         <v>1.4687</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="30" t="n">
         <v>0.3252</v>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" s="31" t="n">
         <v>0.1833</v>
       </c>
-      <c r="F5" s="26" t="n">
+      <c r="F5" s="30" t="n">
         <v>0.4394</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="30" t="n">
         <v>-0.4419</v>
       </c>
     </row>
@@ -5445,19 +5674,19 @@
           <t>Palm Hills Developments</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="29" t="n">
         <v>1.0481</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="30" t="n">
         <v>0.2997</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="31" t="n">
         <v>0.1808</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="30" t="n">
         <v>0.4391</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="30" t="n">
         <v>-0.4866</v>
       </c>
     </row>
@@ -5472,19 +5701,19 @@
           <t>Orascom Development Egypt</t>
         </is>
       </c>
-      <c r="C7" s="31" t="n">
+      <c r="C7" s="29" t="n">
         <v>0.8817</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="30" t="n">
         <v>0.3251</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="31" t="n">
         <v>0.1727</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="30" t="n">
         <v>0.4619</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="30" t="n">
         <v>-0.4293</v>
       </c>
     </row>
@@ -5499,19 +5728,19 @@
           <t>Heliopolis Housing and Development</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="29" t="n">
         <v>0.7648</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="30" t="n">
         <v>0.2874</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="31" t="n">
         <v>0.1803</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="30" t="n">
         <v>0.444</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="30" t="n">
         <v>-0.3958</v>
       </c>
     </row>
@@ -5526,19 +5755,19 @@
           <t>Emaar Misr for Development</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="29" t="n">
         <v>0.7349</v>
       </c>
-      <c r="D9" s="26" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.2423</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="31" t="n">
         <v>0.1693</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="30" t="n">
         <v>0.412</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="30" t="n">
         <v>-0.4712</v>
       </c>
     </row>
@@ -5553,19 +5782,19 @@
           <t>Pioneers Properties for Urban Development</t>
         </is>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="29" t="n">
         <v>0.7006</v>
       </c>
-      <c r="D10" s="26" t="n">
+      <c r="D10" s="30" t="n">
         <v>0.2565</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="31" t="n">
         <v>0.1854</v>
       </c>
-      <c r="F10" s="26" t="n">
+      <c r="F10" s="30" t="n">
         <v>0.4217</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="30" t="n">
         <v>-0.5199</v>
       </c>
     </row>
@@ -5580,24 +5809,24 @@
           <t>Sixth of October Development &amp; Investment (SODIC)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="n">
+      <c r="C11" s="29" t="n">
         <v>0.4949</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="30" t="n">
         <v>0.1018</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="31" t="n">
         <v>0.2275</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="30" t="n">
         <v>0.4755</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="30" t="n">
         <v>-0.4658</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>Earnings and book multiples are not published for the peer group: no peer discloses statements this study can obtain on a consistent basis, and an inconsistent multiple would mislead.</t>
         </is>
@@ -6063,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6402,80 +6631,140 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation, share of revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="n">
+        <v>0.009779011482113282</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>FY2025 as reported: depreciation and amortisation over revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>NOT DISCLOSED — absent by design, never estimated</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Interest-bearing borrowings (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>24069.4</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>the bank and loan lines only, FY2025: a large part of the balance sheet (notes payable to land sellers, customer balances) does not bear interest</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>cash flow statement detail</t>
-        </is>
+          <t>Effective P&amp;L rate on those borrowings</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n">
+        <v>0.1390770023349149</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>PHD's earnings releases publish the cash-flow statement in three totals only — re-verified 17-09-2026 on the 1Q2026 and 4Q2024 releases — and FY2025 has no release at all, so the t</t>
+          <t>FY2025 finance cost over the interest-bearing subset above. NOT the marginal rate: part of the interest incurred is capitalised into work in progress. The charge is held at this level, flat and nominal, for all fifteen years while revenue grows sixfold — the alternative footing is priced in the study's contested-judgement record</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>fy2025 results release</t>
-        </is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n">
+        <v>0.225</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>h1 2026 results</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>PHD's reviewed consolidated statements to 30 June 2026 are REPORTED to have been filed with the Egyptian Exchange on 18 August 2026, and an external audit of this study quotes figu</t>
+          <t>PHD's own tax note computes FY2025 and FY2024 current tax at this rate on net taxable profit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>securitisation pricing</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>NOT DISCLOSED — absent by design, never estimated</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>per project pricing</t>
+          <t>cash flow statement detail</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+          <t>PHD's earnings releases publish the cash-flow statement in three totals only — re-verified 17-09-2026 on the 1Q2026 and 4Q2024 releases — and FY2025 has no release at all, so the t</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t>fy2025 results release</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>h1 2026 results</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>PHD's reviewed consolidated statements to 30 June 2026 are REPORTED to have been filed with the Egyptian Exchange on 18 August 2026, and an external audit of this study quotes figu</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>securitisation pricing</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>per project pricing</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
           <t>backlog cost to complete</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Remaining construction cost against the EGP 263bn backlog is not disclosed as a single figure. It is inferred in the model from the realised gross margin and flagged where used.</t>
         </is>
@@ -8310,7 +8599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -8438,6 +8727,11 @@
       <c r="P5" s="24" t="n">
         <v>5632.6667</v>
       </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>the segment engine; read by nothing that reaches the value</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -8490,6 +8784,11 @@
       <c r="P6" s="24" t="n">
         <v>358306.4853</v>
       </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>the segment engine; read by nothing that reaches the value</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -8497,50 +8796,65 @@
           <t>Units delivered</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
-        <v>2041.734</v>
-      </c>
-      <c r="C7" s="24" t="n">
-        <v>2347.9941</v>
-      </c>
-      <c r="D7" s="24" t="n">
-        <v>2664.9733</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <v>2984.7701</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>3298.171</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>3595.0064</v>
-      </c>
-      <c r="H7" s="24" t="n">
-        <v>3864.6319</v>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>4096.5098</v>
-      </c>
-      <c r="J7" s="24" t="n">
-        <v>4280.8527</v>
-      </c>
-      <c r="K7" s="24" t="n">
-        <v>4409.2783</v>
-      </c>
-      <c r="L7" s="24" t="n">
-        <v>4475.4175</v>
-      </c>
-      <c r="M7" s="24" t="n">
-        <v>4475.4175</v>
-      </c>
-      <c r="N7" s="24" t="n">
-        <v>4475.4175</v>
-      </c>
-      <c r="O7" s="24" t="n">
-        <v>4475.4175</v>
-      </c>
-      <c r="P7" s="24" t="n">
-        <v>4475.4175</v>
+      <c r="B7" s="21">
+        <f>DCF!B7</f>
+        <v/>
+      </c>
+      <c r="C7" s="21">
+        <f>DCF!C7</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>DCF!D7</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>DCF!E7</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>DCF!F7</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>DCF!G7</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>DCF!H7</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>DCF!I7</f>
+        <v/>
+      </c>
+      <c r="J7" s="21">
+        <f>DCF!J7</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>DCF!K7</f>
+        <v/>
+      </c>
+      <c r="L7" s="21">
+        <f>DCF!L7</f>
+        <v/>
+      </c>
+      <c r="M7" s="21">
+        <f>DCF!M7</f>
+        <v/>
+      </c>
+      <c r="N7" s="21">
+        <f>DCF!N7</f>
+        <v/>
+      </c>
+      <c r="O7" s="21">
+        <f>DCF!O7</f>
+        <v/>
+      </c>
+      <c r="P7" s="21">
+        <f>DCF!P7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -8549,50 +8863,65 @@
           <t>Revenue per delivered unit</t>
         </is>
       </c>
-      <c r="B8" s="25" t="n">
-        <v>19.7278</v>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>22.0951</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>24.0837</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>27.7023</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>29.6414</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>31.7163</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>33.9365</v>
-      </c>
-      <c r="J8" s="25" t="n">
-        <v>36.312</v>
-      </c>
-      <c r="K8" s="25" t="n">
-        <v>38.8539</v>
-      </c>
-      <c r="L8" s="25" t="n">
-        <v>41.5737</v>
-      </c>
-      <c r="M8" s="25" t="n">
-        <v>44.4838</v>
-      </c>
-      <c r="N8" s="25" t="n">
-        <v>47.5977</v>
-      </c>
-      <c r="O8" s="25" t="n">
-        <v>50.9295</v>
-      </c>
-      <c r="P8" s="25" t="n">
-        <v>54.4946</v>
+      <c r="B8" s="7">
+        <f>DCF!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="7">
+        <f>DCF!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="7">
+        <f>DCF!D8</f>
+        <v/>
+      </c>
+      <c r="E8" s="7">
+        <f>DCF!E8</f>
+        <v/>
+      </c>
+      <c r="F8" s="7">
+        <f>DCF!F8</f>
+        <v/>
+      </c>
+      <c r="G8" s="7">
+        <f>DCF!G8</f>
+        <v/>
+      </c>
+      <c r="H8" s="7">
+        <f>DCF!H8</f>
+        <v/>
+      </c>
+      <c r="I8" s="7">
+        <f>DCF!I8</f>
+        <v/>
+      </c>
+      <c r="J8" s="7">
+        <f>DCF!J8</f>
+        <v/>
+      </c>
+      <c r="K8" s="7">
+        <f>DCF!K8</f>
+        <v/>
+      </c>
+      <c r="L8" s="7">
+        <f>DCF!L8</f>
+        <v/>
+      </c>
+      <c r="M8" s="7">
+        <f>DCF!M8</f>
+        <v/>
+      </c>
+      <c r="N8" s="7">
+        <f>DCF!N8</f>
+        <v/>
+      </c>
+      <c r="O8" s="7">
+        <f>DCF!O8</f>
+        <v/>
+      </c>
+      <c r="P8" s="7">
+        <f>DCF!P8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -8601,50 +8930,65 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
-        <v>40278.934</v>
-      </c>
-      <c r="C9" s="24" t="n">
-        <v>51879.267</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>64182.4351</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>77275.6519</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>91366.867</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>106561.177</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>122571.9939</v>
-      </c>
-      <c r="I9" s="24" t="n">
-        <v>139021.1555</v>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>155446.505</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>171317.5931</v>
-      </c>
-      <c r="L9" s="24" t="n">
-        <v>186059.472</v>
-      </c>
-      <c r="M9" s="24" t="n">
-        <v>199083.6351</v>
-      </c>
-      <c r="N9" s="24" t="n">
-        <v>213019.4895</v>
-      </c>
-      <c r="O9" s="24" t="n">
-        <v>227930.8538</v>
-      </c>
-      <c r="P9" s="24" t="n">
-        <v>243886.0136</v>
+      <c r="B9" s="21">
+        <f>DCF!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="21">
+        <f>DCF!C9</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>DCF!D9</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>DCF!E9</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>DCF!F9</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>DCF!G9</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>DCF!H9</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>DCF!I9</f>
+        <v/>
+      </c>
+      <c r="J9" s="21">
+        <f>DCF!J9</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>DCF!K9</f>
+        <v/>
+      </c>
+      <c r="L9" s="21">
+        <f>DCF!L9</f>
+        <v/>
+      </c>
+      <c r="M9" s="21">
+        <f>DCF!M9</f>
+        <v/>
+      </c>
+      <c r="N9" s="21">
+        <f>DCF!N9</f>
+        <v/>
+      </c>
+      <c r="O9" s="21">
+        <f>DCF!O9</f>
+        <v/>
+      </c>
+      <c r="P9" s="21">
+        <f>DCF!P9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -8653,50 +8997,70 @@
           <t>Cost per delivered unit</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
-        <v>12.7411</v>
-      </c>
-      <c r="C10" s="25" t="n">
-        <v>14.2701</v>
-      </c>
-      <c r="D10" s="25" t="n">
-        <v>15.5544</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>16.7209</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>17.8914</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>19.1438</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>20.4839</v>
-      </c>
-      <c r="I10" s="25" t="n">
-        <v>21.9177</v>
-      </c>
-      <c r="J10" s="25" t="n">
-        <v>23.452</v>
-      </c>
-      <c r="K10" s="25" t="n">
-        <v>25.0936</v>
-      </c>
-      <c r="L10" s="25" t="n">
-        <v>26.8502</v>
-      </c>
-      <c r="M10" s="25" t="n">
-        <v>28.7297</v>
-      </c>
-      <c r="N10" s="25" t="n">
-        <v>30.7408</v>
-      </c>
-      <c r="O10" s="25" t="n">
-        <v>32.8926</v>
-      </c>
-      <c r="P10" s="25" t="n">
-        <v>35.1951</v>
+      <c r="B10" s="7">
+        <f>B8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="C10" s="7">
+        <f>C8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>D8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E10" s="7">
+        <f>E8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="7">
+        <f>F8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="G10" s="7">
+        <f>G8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="H10" s="7">
+        <f>H8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="I10" s="7">
+        <f>I8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="J10" s="7">
+        <f>J8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="K10" s="7">
+        <f>K8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="L10" s="7">
+        <f>L8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="M10" s="7">
+        <f>M8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="N10" s="7">
+        <f>N8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="O10" s="7">
+        <f>O8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="P10" s="7">
+        <f>P8*(1-Assumptions!$B$8)</f>
+        <v/>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>price per unit times one minus the held margin: no delivered-unit count is published after FY2024, so there is no independent cost per unit to build</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -8705,50 +9069,65 @@
           <t>Cost of revenue</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
-        <v>26013.9771</v>
-      </c>
-      <c r="C11" s="24" t="n">
-        <v>33506.0026</v>
-      </c>
-      <c r="D11" s="24" t="n">
-        <v>41451.9511</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>49908.1491</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>59008.9001</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>68822.08010000001</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>79162.5977</v>
-      </c>
-      <c r="I11" s="24" t="n">
-        <v>89786.21829999999</v>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>100394.46</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>110644.7344</v>
-      </c>
-      <c r="L11" s="24" t="n">
-        <v>120165.7137</v>
-      </c>
-      <c r="M11" s="24" t="n">
-        <v>128577.3137</v>
-      </c>
-      <c r="N11" s="24" t="n">
-        <v>137577.7257</v>
-      </c>
-      <c r="O11" s="24" t="n">
-        <v>147208.1665</v>
-      </c>
-      <c r="P11" s="24" t="n">
-        <v>157512.7381</v>
+      <c r="B11" s="21">
+        <f>B7*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>C7*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>D7*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>E7*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>F7*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>G7*G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>H7*H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>I7*I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="21">
+        <f>J7*J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>K7*K10</f>
+        <v/>
+      </c>
+      <c r="L11" s="21">
+        <f>L7*L10</f>
+        <v/>
+      </c>
+      <c r="M11" s="21">
+        <f>M7*M10</f>
+        <v/>
+      </c>
+      <c r="N11" s="21">
+        <f>N7*N10</f>
+        <v/>
+      </c>
+      <c r="O11" s="21">
+        <f>O7*O10</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>P7*P10</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -8757,50 +9136,65 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
-        <v>14264.9569</v>
-      </c>
-      <c r="C12" s="24" t="n">
-        <v>18373.2644</v>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>22730.4841</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>27367.5028</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>32357.967</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>37739.0969</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>43409.3962</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>49234.9372</v>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>55052.045</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>60672.8588</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>65893.7583</v>
-      </c>
-      <c r="M12" s="24" t="n">
-        <v>70506.3214</v>
-      </c>
-      <c r="N12" s="24" t="n">
-        <v>75441.76390000001</v>
-      </c>
-      <c r="O12" s="24" t="n">
-        <v>80722.68730000001</v>
-      </c>
-      <c r="P12" s="24" t="n">
-        <v>86373.2754</v>
+      <c r="B12" s="21">
+        <f>B9-B11</f>
+        <v/>
+      </c>
+      <c r="C12" s="21">
+        <f>C9-C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>D9-D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>E9-E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>F9-F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>G9-G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>H9-H11</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>I9-I11</f>
+        <v/>
+      </c>
+      <c r="J12" s="21">
+        <f>J9-J11</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>K9-K11</f>
+        <v/>
+      </c>
+      <c r="L12" s="21">
+        <f>L9-L11</f>
+        <v/>
+      </c>
+      <c r="M12" s="21">
+        <f>M9-M11</f>
+        <v/>
+      </c>
+      <c r="N12" s="21">
+        <f>N9-N11</f>
+        <v/>
+      </c>
+      <c r="O12" s="21">
+        <f>O9-O11</f>
+        <v/>
+      </c>
+      <c r="P12" s="21">
+        <f>P9-P11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -8809,50 +9203,70 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="C13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="D13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="E13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="F13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="G13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="H13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="N13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="O13" s="26" t="n">
-        <v>0.3542</v>
-      </c>
-      <c r="P13" s="26" t="n">
-        <v>0.3542</v>
+      <c r="B13" s="17">
+        <f>B12/B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>C12/C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>D12/D9</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>E12/E9</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>F12/F9</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>G12/G9</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>H12/H9</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>I12/I9</f>
+        <v/>
+      </c>
+      <c r="J13" s="17">
+        <f>J12/J9</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>K12/K9</f>
+        <v/>
+      </c>
+      <c r="L13" s="17">
+        <f>L12/L9</f>
+        <v/>
+      </c>
+      <c r="M13" s="17">
+        <f>M12/M9</f>
+        <v/>
+      </c>
+      <c r="N13" s="17">
+        <f>N12/N9</f>
+        <v/>
+      </c>
+      <c r="O13" s="17">
+        <f>O12/O9</f>
+        <v/>
+      </c>
+      <c r="P13" s="17">
+        <f>P12/P9</f>
+        <v/>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>an output of the two rows above, which is what makes it flat: one escalator drives price and cost alike</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -8861,362 +9275,534 @@
           <t>Overheads</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
-        <v>7088.8732</v>
-      </c>
-      <c r="C14" s="24" t="n">
-        <v>9130.468699999999</v>
-      </c>
-      <c r="D14" s="24" t="n">
-        <v>11295.7594</v>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>13600.0943</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>16080.0715</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>18754.1874</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>21572.004</v>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>24466.9669</v>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>27357.7391</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>30150.9642</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>32745.4547</v>
-      </c>
-      <c r="M14" s="24" t="n">
-        <v>35037.6365</v>
-      </c>
-      <c r="N14" s="24" t="n">
-        <v>37490.2711</v>
-      </c>
-      <c r="O14" s="24" t="n">
-        <v>40114.5901</v>
-      </c>
-      <c r="P14" s="24" t="n">
-        <v>42922.6114</v>
+      <c r="B14" s="21">
+        <f>B9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="C14" s="21">
+        <f>C9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>D9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>E9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>F9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>G9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>H9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="I14" s="21">
+        <f>I9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="J14" s="21">
+        <f>J9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>K9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="L14" s="21">
+        <f>L9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="M14" s="21">
+        <f>M9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="N14" s="21">
+        <f>N9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="O14" s="21">
+        <f>O9*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="P14" s="21">
+        <f>P9*Assumptions!$B$9</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Operating profit</t>
-        </is>
-      </c>
-      <c r="B15" s="24" t="n">
-        <v>6782.1955</v>
-      </c>
-      <c r="C15" s="24" t="n">
-        <v>8735.4678</v>
-      </c>
-      <c r="D15" s="24" t="n">
-        <v>10807.084</v>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>13011.7291</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>15384.4179</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>17942.8466</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>20638.7593</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>23408.4808</v>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>26174.1928</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>28846.5778</v>
-      </c>
-      <c r="L15" s="24" t="n">
-        <v>31328.8259</v>
-      </c>
-      <c r="M15" s="24" t="n">
-        <v>33521.8437</v>
-      </c>
-      <c r="N15" s="24" t="n">
-        <v>35868.3727</v>
-      </c>
-      <c r="O15" s="24" t="n">
-        <v>38379.1588</v>
-      </c>
-      <c r="P15" s="24" t="n">
-        <v>41065.6999</v>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B15" s="21">
+        <f>B9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="C15" s="21">
+        <f>C9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>D9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>E9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>F9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>G9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>H9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>I9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="J15" s="21">
+        <f>J9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>K9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="L15" s="21">
+        <f>L9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="M15" s="21">
+        <f>M9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="N15" s="21">
+        <f>N9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="O15" s="21">
+        <f>O9*Assumptions!$B$25</f>
+        <v/>
+      </c>
+      <c r="P15" s="21">
+        <f>P9*Assumptions!$B$25</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Finance cost</t>
-        </is>
-      </c>
-      <c r="B16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="L16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="M16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="N16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="O16" s="24" t="n">
-        <v>3347.5</v>
-      </c>
-      <c r="P16" s="24" t="n">
-        <v>3347.5</v>
+          <t>Operating profit</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f>B12-B14-B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="21">
+        <f>C12-C14-C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>D12-D14-D15</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>E12-E14-E15</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>F12-F14-F15</f>
+        <v/>
+      </c>
+      <c r="G16" s="21">
+        <f>G12-G14-G15</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>H12-H14-H15</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>I12-I14-I15</f>
+        <v/>
+      </c>
+      <c r="J16" s="21">
+        <f>J12-J14-J15</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>K12-K14-K15</f>
+        <v/>
+      </c>
+      <c r="L16" s="21">
+        <f>L12-L14-L15</f>
+        <v/>
+      </c>
+      <c r="M16" s="21">
+        <f>M12-M14-M15</f>
+        <v/>
+      </c>
+      <c r="N16" s="21">
+        <f>N12-N14-N15</f>
+        <v/>
+      </c>
+      <c r="O16" s="21">
+        <f>O12-O14-O15</f>
+        <v/>
+      </c>
+      <c r="P16" s="21">
+        <f>P12-P14-P15</f>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Finance cost</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="C17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="G17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="J17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="L17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="M17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="N17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="O17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="P17" s="21">
+        <f>Assumptions!$B$26*Assumptions!$B$27</f>
+        <v/>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>the interest-bearing subset times its effective rate, HELD FLAT AND NOMINAL for all fifteen years while revenue grows sixfold; the alternative footing is priced in the study's contested-judgement record</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
-        <v>3434.6955</v>
-      </c>
-      <c r="C17" s="24" t="n">
-        <v>5387.9678</v>
-      </c>
-      <c r="D17" s="24" t="n">
-        <v>7459.584</v>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>9664.2291</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>12036.9179</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>14595.3466</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>17291.2593</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>20060.9808</v>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>22826.6928</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>25499.0778</v>
-      </c>
-      <c r="L17" s="24" t="n">
-        <v>27981.3259</v>
-      </c>
-      <c r="M17" s="24" t="n">
-        <v>30174.3437</v>
-      </c>
-      <c r="N17" s="24" t="n">
-        <v>32520.8727</v>
-      </c>
-      <c r="O17" s="24" t="n">
-        <v>35031.6588</v>
-      </c>
-      <c r="P17" s="24" t="n">
-        <v>37718.1999</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B18" s="21">
+        <f>B16-B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="21">
+        <f>C16-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>D16-D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>E16-E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>F16-F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="21">
+        <f>G16-G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>H16-H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>I16-I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="21">
+        <f>J16-J17</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>K16-K17</f>
+        <v/>
+      </c>
+      <c r="L18" s="21">
+        <f>L16-L17</f>
+        <v/>
+      </c>
+      <c r="M18" s="21">
+        <f>M16-M17</f>
+        <v/>
+      </c>
+      <c r="N18" s="21">
+        <f>N16-N17</f>
+        <v/>
+      </c>
+      <c r="O18" s="21">
+        <f>O16-O17</f>
+        <v/>
+      </c>
+      <c r="P18" s="21">
+        <f>P16-P17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Net profit</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
-        <v>2661.889</v>
-      </c>
-      <c r="C18" s="24" t="n">
-        <v>4175.675</v>
-      </c>
-      <c r="D18" s="24" t="n">
-        <v>5781.1776</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>7489.7775</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>9328.6114</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>11311.3936</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>13400.7259</v>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>15547.2601</v>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>17690.6869</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>19761.7853</v>
-      </c>
-      <c r="L18" s="24" t="n">
-        <v>21685.5275</v>
-      </c>
-      <c r="M18" s="24" t="n">
-        <v>23385.1163</v>
-      </c>
-      <c r="N18" s="24" t="n">
-        <v>25203.6764</v>
-      </c>
-      <c r="O18" s="24" t="n">
-        <v>27149.5356</v>
-      </c>
-      <c r="P18" s="24" t="n">
-        <v>29231.6049</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Earnings per share (EGP)</t>
-        </is>
-      </c>
-      <c r="B19" s="25" t="n">
-        <v>0.9308</v>
-      </c>
-      <c r="C19" s="25" t="n">
-        <v>1.4601</v>
-      </c>
-      <c r="D19" s="25" t="n">
-        <v>2.0214</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>2.6189</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>3.2618</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>3.9551</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>4.6857</v>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>5.4363</v>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>6.1857</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>6.9099</v>
-      </c>
-      <c r="L19" s="25" t="n">
-        <v>7.5826</v>
-      </c>
-      <c r="M19" s="25" t="n">
-        <v>8.1768</v>
-      </c>
-      <c r="N19" s="25" t="n">
-        <v>8.8127</v>
-      </c>
-      <c r="O19" s="25" t="n">
-        <v>9.4931</v>
-      </c>
-      <c r="P19" s="25" t="n">
-        <v>10.2211</v>
+      <c r="B19" s="21">
+        <f>B18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="C19" s="21">
+        <f>C18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>D18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
+        <f>E18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>F18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="G19" s="21">
+        <f>G18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>H18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="I19" s="21">
+        <f>I18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="J19" s="21">
+        <f>J18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>K18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="L19" s="21">
+        <f>L18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="M19" s="21">
+        <f>M18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="N19" s="21">
+        <f>N18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="O19" s="21">
+        <f>O18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="P19" s="21">
+        <f>P18*(1-Assumptions!$B$28)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>pre-tax profit is positive in every forecast year, so this is the tax charge the model applies</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>Earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>B19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="C20" s="7">
+        <f>C19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="D20" s="7">
+        <f>D19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="E20" s="7">
+        <f>E19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="F20" s="7">
+        <f>F19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="G20" s="7">
+        <f>G19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="H20" s="7">
+        <f>H19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="I20" s="7">
+        <f>I19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="J20" s="7">
+        <f>J19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="K20" s="7">
+        <f>K19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="L20" s="7">
+        <f>L19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="M20" s="7">
+        <f>M19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="N20" s="7">
+        <f>N19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="O20" s="7">
+        <f>O19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+      <c r="P20" s="7">
+        <f>P19/Assumptions!$B$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>Order book, closing</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B21" s="24" t="n">
         <v>352433.0582</v>
       </c>
-      <c r="C20" s="24" t="n">
+      <c r="C21" s="24" t="n">
         <v>445831.2225</v>
       </c>
-      <c r="D20" s="24" t="n">
+      <c r="D21" s="24" t="n">
         <v>540001.1874000001</v>
       </c>
-      <c r="E20" s="24" t="n">
+      <c r="E21" s="24" t="n">
         <v>632954.3656</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F21" s="24" t="n">
         <v>723732.3467</v>
       </c>
-      <c r="G20" s="24" t="n">
+      <c r="G21" s="24" t="n">
         <v>812066.1572</v>
       </c>
-      <c r="H20" s="24" t="n">
+      <c r="H21" s="24" t="n">
         <v>898031.8</v>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I21" s="24" t="n">
         <v>982145.9158</v>
       </c>
-      <c r="J20" s="24" t="n">
+      <c r="J21" s="24" t="n">
         <v>1065454.1511</v>
       </c>
-      <c r="K20" s="24" t="n">
+      <c r="K21" s="24" t="n">
         <v>1149604.13</v>
       </c>
-      <c r="L20" s="24" t="n">
+      <c r="L21" s="24" t="n">
         <v>1236894.9601</v>
       </c>
-      <c r="M20" s="24" t="n">
+      <c r="M21" s="24" t="n">
         <v>1330296.1483</v>
       </c>
-      <c r="N20" s="24" t="n">
+      <c r="N21" s="24" t="n">
         <v>1430235.4196</v>
       </c>
-      <c r="O20" s="24" t="n">
+      <c r="O21" s="24" t="n">
         <v>1537170.44</v>
       </c>
-      <c r="P20" s="24" t="n">
+      <c r="P21" s="24" t="n">
         <v>1651590.9118</v>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>rolls the segment engine's new sales behind revenue; read by nothing that reaches the value</t>
+        </is>
       </c>
     </row>
   </sheetData>
